--- a/data/trans_dic/P2B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,41; 25,69</t>
+          <t>18,53; 25,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,0; 57,01</t>
+          <t>48,7; 56,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,97; 53,09</t>
+          <t>44,49; 53,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,28; 28,28</t>
+          <t>19,73; 28,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,66; 29,99</t>
+          <t>22,34; 29,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,29; 59,42</t>
+          <t>51,05; 59,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,07; 52,27</t>
+          <t>44,41; 52,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,81; 27,66</t>
+          <t>17,45; 27,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,79; 26,9</t>
+          <t>21,7; 26,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51,2; 57,05</t>
+          <t>51,13; 57,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,49; 51,72</t>
+          <t>45,4; 51,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,38; 26,6</t>
+          <t>19,74; 26,66</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,69; 25,93</t>
+          <t>19,74; 25,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,24; 58,51</t>
+          <t>51,42; 58,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,13; 47,33</t>
+          <t>39,72; 47,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,07; 29,41</t>
+          <t>22,04; 29,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,15; 28,88</t>
+          <t>23,0; 29,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,12; 59,61</t>
+          <t>53,23; 59,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,33; 52,79</t>
+          <t>46,03; 52,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,65; 36,37</t>
+          <t>30,63; 36,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,97; 26,42</t>
+          <t>21,91; 26,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,33; 58,22</t>
+          <t>53,27; 58,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,42; 49,41</t>
+          <t>44,54; 49,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,73; 32,39</t>
+          <t>27,64; 32,24</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,63; 25,14</t>
+          <t>17,76; 25,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,57; 59,33</t>
+          <t>50,93; 59,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,94; 38,36</t>
+          <t>29,91; 38,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,88; 26,18</t>
+          <t>17,97; 26,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 29,18</t>
+          <t>21,9; 29,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,75; 62,08</t>
+          <t>54,22; 61,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,85; 45,03</t>
+          <t>37,52; 45,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,9; 73,87</t>
+          <t>21,04; 73,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,14; 26,11</t>
+          <t>20,78; 26,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,61; 59,41</t>
+          <t>53,82; 59,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,11; 40,65</t>
+          <t>34,88; 40,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,05; 59,59</t>
+          <t>21,19; 60,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,06; 24,54</t>
+          <t>18,39; 24,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,26; 48,74</t>
+          <t>41,21; 48,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,89; 43,89</t>
+          <t>36,47; 44,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,2; 23,5</t>
+          <t>17,29; 23,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,94; 30,21</t>
+          <t>24,28; 30,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,92; 51,53</t>
+          <t>44,86; 51,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,17; 51,25</t>
+          <t>44,26; 51,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,47; 25,77</t>
+          <t>16,0; 25,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,52; 26,81</t>
+          <t>22,42; 26,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44,16; 49,04</t>
+          <t>44,09; 49,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42,08; 47,2</t>
+          <t>41,92; 47,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,1; 23,86</t>
+          <t>17,95; 23,68</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,24; 23,52</t>
+          <t>20,23; 23,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,81; 53,79</t>
+          <t>49,74; 53,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,52; 43,46</t>
+          <t>39,73; 43,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,13; 24,95</t>
+          <t>21,06; 24,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,72; 27,85</t>
+          <t>24,54; 27,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,36; 55,89</t>
+          <t>52,24; 55,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,1; 48,91</t>
+          <t>45,12; 48,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,01; 46,79</t>
+          <t>25,08; 47,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,03; 25,45</t>
+          <t>23,06; 25,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51,69; 54,52</t>
+          <t>51,7; 54,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43,1; 45,9</t>
+          <t>43,2; 45,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,99; 38,28</t>
+          <t>23,9; 38,44</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97656; 136251</t>
+          <t>98259; 136280</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>288442; 335629</t>
+          <t>286694; 335216</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>222626; 268828</t>
+          <t>225300; 269318</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85895; 119802</t>
+          <t>83555; 119100</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>133137; 176196</t>
+          <t>131267; 172080</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>316419; 366594</t>
+          <t>314919; 364604</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>246350; 292163</t>
+          <t>248249; 293233</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>101643; 157868</t>
+          <t>99580; 155920</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>243620; 300766</t>
+          <t>242571; 298470</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>617234; 687794</t>
+          <t>616398; 689275</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>484634; 551009</t>
+          <t>483655; 549049</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>202702; 264475</t>
+          <t>196314; 265057</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>147235; 193836</t>
+          <t>147572; 193840</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>421377; 481133</t>
+          <t>422828; 483083</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>305508; 360351</t>
+          <t>302393; 361732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>140914; 187832</t>
+          <t>140747; 188639</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>195949; 244536</t>
+          <t>194743; 246826</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>488176; 547896</t>
+          <t>489185; 549638</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>417219; 475369</t>
+          <t>414502; 476676</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>228710; 271332</t>
+          <t>228508; 271514</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>350199; 421187</t>
+          <t>349270; 424594</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>928702; 1013787</t>
+          <t>927590; 1012778</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>738281; 821186</t>
+          <t>740223; 818550</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>383929; 448559</t>
+          <t>382769; 446459</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>90597; 129184</t>
+          <t>91281; 128871</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>297808; 349394</t>
+          <t>299899; 350985</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>163619; 209630</t>
+          <t>163428; 211200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87126; 127601</t>
+          <t>87589; 128159</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>128339; 170075</t>
+          <t>127624; 169927</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>369923; 427255</t>
+          <t>373140; 424798</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>235832; 288178</t>
+          <t>240132; 289339</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>163599; 578370</t>
+          <t>164740; 577494</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>231801; 286343</t>
+          <t>227862; 285930</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>684711; 758764</t>
+          <t>687333; 761556</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>416487; 482215</t>
+          <t>413807; 481821</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>267369; 756915</t>
+          <t>269133; 766872</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121507; 165082</t>
+          <t>123677; 165190</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>308810; 364763</t>
+          <t>308401; 365182</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>252628; 300574</t>
+          <t>249749; 301625</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>106622; 145667</t>
+          <t>107178; 147523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>205025; 258727</t>
+          <t>207928; 260565</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>412987; 473739</t>
+          <t>412430; 477110</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>377075; 437486</t>
+          <t>377874; 438486</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>145719; 214895</t>
+          <t>133447; 211430</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>344286; 409924</t>
+          <t>342799; 409031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>736406; 817812</t>
+          <t>735270; 820225</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>647463; 726228</t>
+          <t>645000; 724489</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>263167; 346920</t>
+          <t>260888; 344217</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>498707; 579750</t>
+          <t>498664; 585848</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1368979; 1478154</t>
+          <t>1366860; 1474978</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>987571; 1086042</t>
+          <t>992738; 1089928</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>458338; 541364</t>
+          <t>456947; 536612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>710346; 800129</t>
+          <t>705160; 801015</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1645976; 1756874</t>
+          <t>1642075; 1759869</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1331846; 1444516</t>
+          <t>1332406; 1446870</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>733652; 1372674</t>
+          <t>735655; 1404661</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1229084; 1358587</t>
+          <t>1231143; 1358193</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3045590; 3212455</t>
+          <t>3046118; 3207681</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2350037; 2502291</t>
+          <t>2355148; 2502314</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1224278; 1953711</t>
+          <t>1219515; 1961677</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,53; 25,7</t>
+          <t>18,74; 25,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,7; 56,94</t>
+          <t>48,61; 57,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,49; 53,19</t>
+          <t>44,33; 53,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,73; 28,12</t>
+          <t>19,97; 28,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,34; 29,29</t>
+          <t>22,35; 29,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,05; 59,1</t>
+          <t>50,94; 59,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,41; 52,46</t>
+          <t>44,63; 53,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,45; 27,32</t>
+          <t>22,9; 28,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,7; 26,7</t>
+          <t>21,71; 26,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51,13; 57,17</t>
+          <t>51,03; 57,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,4; 51,54</t>
+          <t>45,53; 51,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,74; 26,66</t>
+          <t>22,69; 27,73</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,74; 25,93</t>
+          <t>19,86; 25,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,42; 58,75</t>
+          <t>51,17; 58,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,72; 47,51</t>
+          <t>40,16; 47,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,04; 29,54</t>
+          <t>24,6; 31,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,0; 29,15</t>
+          <t>22,57; 28,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,23; 59,8</t>
+          <t>53,11; 60,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,03; 52,93</t>
+          <t>46,3; 52,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,63; 36,39</t>
+          <t>30,64; 36,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,91; 26,63</t>
+          <t>22,23; 26,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,27; 58,16</t>
+          <t>53,29; 58,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,54; 49,25</t>
+          <t>44,35; 49,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,64; 32,24</t>
+          <t>28,58; 33,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,76; 25,08</t>
+          <t>17,67; 24,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,93; 59,6</t>
+          <t>50,7; 59,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,91; 38,65</t>
+          <t>29,98; 38,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,97; 26,3</t>
+          <t>18,35; 26,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,9; 29,16</t>
+          <t>21,78; 29,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,22; 61,72</t>
+          <t>54,12; 62,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,52; 45,21</t>
+          <t>37,29; 45,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,04; 73,76</t>
+          <t>21,08; 27,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,78; 26,07</t>
+          <t>20,8; 26,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,82; 59,63</t>
+          <t>53,74; 59,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,88; 40,61</t>
+          <t>34,89; 40,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,19; 60,37</t>
+          <t>20,85; 25,78</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,39; 24,56</t>
+          <t>17,94; 24,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,21; 48,8</t>
+          <t>41,53; 48,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,47; 44,05</t>
+          <t>36,49; 43,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,29; 23,8</t>
+          <t>18,08; 24,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,28; 30,42</t>
+          <t>24,3; 30,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,86; 51,9</t>
+          <t>45,37; 51,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,26; 51,36</t>
+          <t>44,27; 51,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,0; 25,35</t>
+          <t>23,41; 28,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,42; 26,75</t>
+          <t>22,47; 26,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44,09; 49,18</t>
+          <t>44,37; 49,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,92; 47,09</t>
+          <t>42,02; 47,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,95; 23,68</t>
+          <t>22,01; 25,99</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,23; 23,77</t>
+          <t>20,06; 23,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,74; 53,67</t>
+          <t>49,73; 53,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,73; 43,61</t>
+          <t>39,59; 43,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,06; 24,74</t>
+          <t>22,17; 25,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,54; 27,88</t>
+          <t>24,55; 27,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,24; 55,98</t>
+          <t>52,37; 55,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,12; 48,99</t>
+          <t>45,03; 48,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,08; 47,88</t>
+          <t>26,41; 29,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,06; 25,44</t>
+          <t>23,05; 25,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51,7; 54,44</t>
+          <t>51,58; 54,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43,2; 45,9</t>
+          <t>43,03; 45,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,9; 38,44</t>
+          <t>24,95; 27,22</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101088</t>
+          <t>109490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>136452</t>
+          <t>148346</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>237541</t>
+          <t>257836</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98259; 136280</t>
+          <t>99405; 136998</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>286694; 335216</t>
+          <t>286149; 336288</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>225300; 269318</t>
+          <t>224443; 269381</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83555; 119100</t>
+          <t>91690; 129589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>131267; 172080</t>
+          <t>131340; 173487</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>314919; 364604</t>
+          <t>314245; 367659</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>248249; 293233</t>
+          <t>249490; 299992</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>99580; 155920</t>
+          <t>130626; 164695</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>242571; 298470</t>
+          <t>242692; 298568</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>616398; 689275</t>
+          <t>615175; 688235</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>483655; 549049</t>
+          <t>485012; 548254</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>196314; 265057</t>
+          <t>233600; 285526</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163817</t>
+          <t>197036</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>249692</t>
+          <t>279379</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>413509</t>
+          <t>476415</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>147572; 193840</t>
+          <t>148477; 194054</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422828; 483083</t>
+          <t>420738; 482720</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>302393; 361732</t>
+          <t>305744; 358885</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>140747; 188639</t>
+          <t>173178; 225201</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>194743; 246826</t>
+          <t>191036; 243920</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>489185; 549638</t>
+          <t>488106; 552930</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>414502; 476676</t>
+          <t>416932; 476865</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>228508; 271514</t>
+          <t>256929; 303942</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>349270; 424594</t>
+          <t>354376; 426757</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>927590; 1012778</t>
+          <t>927974; 1015504</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>740223; 818550</t>
+          <t>737057; 819824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>382769; 446459</t>
+          <t>440893; 513511</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106376</t>
+          <t>123968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>333130</t>
+          <t>155875</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>439505</t>
+          <t>279843</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91281; 128871</t>
+          <t>90789; 127393</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>299899; 350985</t>
+          <t>298571; 349950</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>163428; 211200</t>
+          <t>163815; 209499</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87589; 128159</t>
+          <t>102381; 146015</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>127624; 169927</t>
+          <t>126933; 169415</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>373140; 424798</t>
+          <t>372506; 427143</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>240132; 289339</t>
+          <t>238669; 289831</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>164740; 577494</t>
+          <t>135819; 179858</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>227862; 285930</t>
+          <t>228084; 287424</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>687333; 761556</t>
+          <t>686380; 761238</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>413807; 481821</t>
+          <t>413925; 482118</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>269133; 766872</t>
+          <t>250600; 309932</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124889</t>
+          <t>140755</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>185687</t>
+          <t>214931</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>310576</t>
+          <t>355686</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>123677; 165190</t>
+          <t>120685; 163154</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>308401; 365182</t>
+          <t>310837; 365047</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>249749; 301625</t>
+          <t>249905; 300436</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107178; 147523</t>
+          <t>118365; 161942</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>207928; 260565</t>
+          <t>208115; 260418</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>412430; 477110</t>
+          <t>417127; 475845</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>377874; 438486</t>
+          <t>377928; 436461</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>133447; 211430</t>
+          <t>193870; 238382</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>342799; 409031</t>
+          <t>343594; 410980</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>735270; 820225</t>
+          <t>739912; 820034</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>645000; 724489</t>
+          <t>646545; 725271</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>260888; 344217</t>
+          <t>326320; 385307</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>496170</t>
+          <t>571250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>904961</t>
+          <t>798531</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1401131</t>
+          <t>1369781</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>498664; 585848</t>
+          <t>494437; 581117</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1366860; 1474978</t>
+          <t>1366682; 1477050</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>992738; 1089928</t>
+          <t>989298; 1093685</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>456947; 536612</t>
+          <t>526661; 616392</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>705160; 801015</t>
+          <t>705373; 797847</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1642075; 1759869</t>
+          <t>1646138; 1755358</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1332406; 1446870</t>
+          <t>1329864; 1438320</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>735655; 1404661</t>
+          <t>761055; 840593</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1231143; 1358193</t>
+          <t>1230628; 1358434</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3046118; 3207681</t>
+          <t>3038954; 3202251</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2355148; 2502314</t>
+          <t>2346271; 2495542</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1219515; 1961677</t>
+          <t>1311410; 1430828</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
